--- a/backtest_runs/20260410_193731/by_symbol/GHGL/GHGL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GHGL/GHGL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-2545.140000000004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>97454.86</v>
@@ -633,7 +633,7 @@
         <v>-3654.559999999992</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>95399.17</v>
@@ -679,7 +679,7 @@
         <v>-9430.070000000002</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>85969.10000000001</v>
@@ -909,7 +909,7 @@
         <v>-3654.560000000003</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>92756.14</v>
@@ -1047,7 +1047,7 @@
         <v>-293.6699999999996</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>94681.31</v>
@@ -1185,7 +1185,7 @@
         <v>-2969.33</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>96051.77</v>
@@ -1231,7 +1231,7 @@
         <v>-65.25999999999861</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>95986.51000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-2969.33</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>93017.18000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-1631.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>102936.7</v>
@@ -1461,7 +1461,7 @@
         <v>-3197.73999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>99738.96000000001</v>
@@ -1553,7 +1553,7 @@
         <v>-424.1900000000084</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>100717.86</v>
